--- a/output/pdf_financials_xlsx/CNR.xlsx
+++ b/output/pdf_financials_xlsx/CNR.xlsx
@@ -2560,7 +2560,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>490</v>
@@ -2696,7 +2696,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>490</v>
@@ -3512,7 +3512,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>693</v>
+        <v>712</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>325</v>
@@ -46749,7 +46749,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>CashEquivalents</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">

--- a/output/pdf_financials_xlsx/CNR.xlsx
+++ b/output/pdf_financials_xlsx/CNR.xlsx
@@ -68802,7 +68802,7 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
@@ -69769,7 +69769,7 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
@@ -79398,7 +79398,7 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
@@ -89272,7 +89272,7 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
@@ -91819,7 +91819,7 @@
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E760" s="5" t="n">

--- a/output/pdf_financials_xlsx/CNR.xlsx
+++ b/output/pdf_financials_xlsx/CNR.xlsx
@@ -1447,19 +1447,19 @@
         <v>1287</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>395</v>
+        <v>-395</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-1354</v>
+        <v>1354</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-1213</v>
+        <v>1213</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>976</v>
+        <v>73</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>1443</v>
+        <v>544</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>-1443</v>
@@ -2452,10 +2452,10 @@
         <v>22.34297292319027</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>21.58814421588144</v>
+        <v>1.61468701614687</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>22.75307473982971</v>
+        <v>8.577735730053611</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>21.33668490314949</v>
@@ -4857,10 +4857,10 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="E67" s="3" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>0</v>
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="E68" s="3" t="n">
         <v>0</v>
@@ -4937,10 +4937,10 @@
         <v>0</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="I68" s="3" t="n">
         <v>0</v>
@@ -5404,7 +5404,7 @@
         <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>1167</v>
+        <v>972</v>
       </c>
       <c r="E75" s="3" t="n">
         <v>1366</v>
@@ -5413,10 +5413,10 @@
         <v>1580</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>1626</v>
+        <v>1491</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>1477</v>
+        <v>1321</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>1657</v>
@@ -8569,52 +8569,52 @@
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>0</v>
+        <v>-1584</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-1021</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>0</v>
+        <v>-913</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>0</v>
+        <v>-1420</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-1400</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>0</v>
+        <v>-1400</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>0</v>
+        <v>-1505</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0</v>
+        <v>-1742</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-1992</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>0</v>
+        <v>-2016</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>0</v>
+        <v>-1700</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>0</v>
+        <v>-379</v>
       </c>
       <c r="P121" s="3" t="n">
-        <v>0</v>
+        <v>-1582</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>0</v>
+        <v>-4709</v>
       </c>
       <c r="R121" s="1" t="inlineStr">
         <is>
@@ -54568,7 +54568,11 @@
           <t>Repurchase of common shares (Note 19)</t>
         </is>
       </c>
-      <c r="D413" t="inlineStr"/>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E413" t="inlineStr">
         <is>
           <t>-</t>
@@ -57036,7 +57040,11 @@
           <t>Repurchase of common shares (Note 16)</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E437" t="inlineStr">
         <is>
           <t>-</t>
@@ -58730,7 +58738,11 @@
           <t>Repurchase of common shares (Note 13)</t>
         </is>
       </c>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E453" t="inlineStr">
         <is>
           <t>-</t>
@@ -62375,7 +62387,11 @@
           <t>Repurchase of common shares (Note 9)</t>
         </is>
       </c>
-      <c r="D488" t="inlineStr"/>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E488" t="inlineStr">
         <is>
           <t>-</t>
@@ -63451,7 +63467,11 @@
           <t>Repurchase of common shares (Note 10)</t>
         </is>
       </c>
-      <c r="D498" t="inlineStr"/>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E498" s="5" t="n">
         <v>-1584</v>
       </c>
@@ -93485,7 +93505,11 @@
           <t>Income tax recovery (expense) (1)</t>
         </is>
       </c>
-      <c r="D776" t="inlineStr"/>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E776" t="inlineStr">
         <is>
           <t>-</t>
@@ -94333,7 +94357,11 @@
           <t>Income tax recovery (expense) (Note 6)</t>
         </is>
       </c>
-      <c r="D784" t="inlineStr"/>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E784" t="inlineStr">
         <is>
           <t>-</t>
@@ -95147,7 +95175,11 @@
           <t>Income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D792" t="inlineStr"/>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E792" t="inlineStr">
         <is>
           <t>-</t>
@@ -95652,7 +95684,11 @@
           <t>Income tax recovery (expense) (Note 4)</t>
         </is>
       </c>
-      <c r="D797" t="inlineStr"/>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E797" t="inlineStr">
         <is>
           <t>-</t>
@@ -96290,7 +96326,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D803" t="inlineStr"/>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E803" t="inlineStr">
         <is>
           <t>-</t>
